--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\MYSELF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF442DDF-FE73-4D6D-8150-87F2F4B72078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ED592D-8B4D-42B7-A692-A660592CEBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A9B6BBD-B787-4672-8FCE-7FD02B8C41F3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>LABEL</t>
   </si>
@@ -82,10 +82,6 @@
 Cross coverage to check relationship between BURST and LEN</t>
   </si>
   <si>
-    <t>compare transfer using 
-ref model and actual transfer</t>
-  </si>
-  <si>
     <t>ID belongs to between 0 - 255
 Same ID transactions WRITE RESPONSE CHANNEL and READ DATA CHANNEL must be properly returned to order of issue 
 Different ID transactions WRITE RESPONSE and READ DATA CHANNEL could be returned to any order of issue</t>
@@ -95,9 +91,6 @@
   </si>
   <si>
     <t>Define coverpoint of AWID, ARID, BID, RID</t>
-  </si>
-  <si>
-    <t>Using ASSOCIATIVE ARRAY to store transaction and compare</t>
   </si>
   <si>
     <t>ID 
@@ -133,9 +126,37 @@
     <t>Define coverpoint of BRESP, RRESP</t>
   </si>
   <si>
+    <t>APB Interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
+PENABLE and PSEL deassert when PREADY is HIGH
+</t>
+  </si>
+  <si>
+    <t>APB Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSLVERR could be OKAY or ERROR
+</t>
+  </si>
+  <si>
+    <t>Random PSLVERR as returning reponse</t>
+  </si>
+  <si>
+    <t>APB Address</t>
+  </si>
+  <si>
+    <t>PADDR is ONLY aligned address</t>
+  </si>
+  <si>
+    <t>Concurrent Assertion 
+(overlapped assertion)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Design supports aligned and unaligned transaction 
-in INCR and WRAP burst
+in INCR burst
 </t>
     </r>
     <r>
@@ -225,31 +246,8 @@
     </r>
   </si>
   <si>
-    <t>APB Interface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
-PENABLE and PSEL deassert when PREADY is HIGH
-</t>
-  </si>
-  <si>
-    <t>APB Response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSLVERR could be OKAY or ERROR
-</t>
-  </si>
-  <si>
-    <t>Random PSLVERR as returning reponse</t>
-  </si>
-  <si>
-    <t>APB Address</t>
-  </si>
-  <si>
-    <t>PADDR is ONLY aligned address</t>
-  </si>
-  <si>
-    <t>Immediate Assertion</t>
+    <t>using ASSOCIATE ARRAY to store and compare transaction
+in Scoreboard</t>
   </si>
 </sst>
 </file>
@@ -294,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -375,11 +373,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -431,6 +453,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,63 +852,61 @@
       <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
+      <c r="E3" s="20" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="121.8" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" ht="69.599999999999994" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="139.19999999999999" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:5" ht="52.2" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -887,28 +916,28 @@
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.35">
       <c r="A9" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>34</v>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
@@ -919,6 +948,9 @@
       <c r="E10" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E3:E6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\MYSELF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95ED592D-8B4D-42B7-A692-A660592CEBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2EB21F-7C28-43D8-B218-A1E788A15F1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A9B6BBD-B787-4672-8FCE-7FD02B8C41F3}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -110,54 +99,145 @@
     <t>Response</t>
   </si>
   <si>
-    <t>Design supports 
+    <t>Directed test to check each response type</t>
+  </si>
+  <si>
+    <t>Define coverpoint of BRESP, RRESP</t>
+  </si>
+  <si>
+    <t>APB Interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
+PENABLE and PSEL deassert when PREADY is HIGH
+</t>
+  </si>
+  <si>
+    <t>APB Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSLVERR could be OKAY or ERROR
+</t>
+  </si>
+  <si>
+    <t>Random PSLVERR as returning reponse</t>
+  </si>
+  <si>
+    <t>APB Address</t>
+  </si>
+  <si>
+    <t>PADDR is ONLY aligned address</t>
+  </si>
+  <si>
+    <t>Concurrent Assertion 
+(overlapped assertion)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Design supports aligned and unaligned transaction 
+in INCR burst
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>First beat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in burst </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>could</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> be unaligned address 
+and all </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remaining beats</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>must</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> be aligned address</t>
+    </r>
+  </si>
+  <si>
+    <t>using ASSOCIATE ARRAY to store and compare transaction
+in Scoreboard</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Design supports 
 OKAY,  SLVERR, DECERR response
 Design supports 4 APB slaves 
 APB1: 32'h0000_0000 - 32'h0000_0FFF
 APB2: 32'h0000_1000 - 32'h0000_1FFF
 APB3: 32'h0000_2000 - 32'h0000_2FFF
 APB4: 32'h0000_3000 - 32'h0000_3FFF
-4-byte transfer</t>
-  </si>
-  <si>
-    <t>Directed test to check each response type</t>
-  </si>
-  <si>
-    <t>Define coverpoint of BRESP, RRESP</t>
-  </si>
-  <si>
-    <t>APB Interface</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
-PENABLE and PSEL deassert when PREADY is HIGH
 </t>
-  </si>
-  <si>
-    <t>APB Response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSLVERR could be OKAY or ERROR
-</t>
-  </si>
-  <si>
-    <t>Random PSLVERR as returning reponse</t>
-  </si>
-  <si>
-    <t>APB Address</t>
-  </si>
-  <si>
-    <t>PADDR is ONLY aligned address</t>
-  </si>
-  <si>
-    <t>Concurrent Assertion 
-(overlapped assertion)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Design supports aligned and unaligned transaction 
-in INCR burst
-</t>
     </r>
     <r>
       <rPr>
@@ -165,42 +245,40 @@
         <sz val="13"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>First beat</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in burst </t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Address outside</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> those ranges -&gt; </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>could</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> be unaligned address 
-and all </t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECERR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Valid Address but SIZE is </t>
     </r>
     <r>
       <rPr>
@@ -208,20 +286,19 @@
         <sz val="13"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>remaining beats</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not 4-byte transfer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -229,32 +306,77 @@
         <sz val="13"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>must</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> be aligned address</t>
-    </r>
-  </si>
-  <si>
-    <t>using ASSOCIATE ARRAY to store and compare transaction
-in Scoreboard</t>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unaligned address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FIXED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WRAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSLVERR</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +397,20 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -798,16 +934,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{676EAC3C-D51A-4C9A-9C98-285499BC1E5A}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="2" max="2" width="53.21875" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
-    <col min="4" max="4" width="48.21875" customWidth="1"/>
-    <col min="5" max="5" width="31.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.796875" customWidth="1"/>
+    <col min="2" max="2" width="53.19921875" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" customWidth="1"/>
+    <col min="4" max="4" width="48.19921875" customWidth="1"/>
+    <col min="5" max="5" width="31.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30" customHeight="1" thickBot="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -824,7 +960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="52.2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="50.4">
       <c r="A2" s="15" t="s">
         <v>5</v>
       </c>
@@ -839,7 +975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="81.599999999999994" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>9</v>
       </c>
@@ -853,10 +989,10 @@
         <v>12</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="121.8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="117.6">
       <c r="A4" s="17" t="s">
         <v>16</v>
       </c>
@@ -871,12 +1007,12 @@
       </c>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="69.599999999999994" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="67.2">
       <c r="A5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -886,27 +1022,27 @@
       </c>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="139.19999999999999" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="184.8">
       <c r="A6" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:5" ht="52.2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="67.2">
       <c r="A7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -914,33 +1050,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="39" customHeight="1">
       <c r="A8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="34.799999999999997" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="33.6">
       <c r="A9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="16.8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -952,5 +1088,6 @@
     <mergeCell ref="E3:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\MYSELF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2EB21F-7C28-43D8-B218-A1E788A15F1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144C995C-99A1-4D0D-B2DD-BE57CB2B1C90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A9B6BBD-B787-4672-8FCE-7FD02B8C41F3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>LABEL</t>
   </si>
@@ -108,11 +108,6 @@
     <t>APB Interface</t>
   </si>
   <si>
-    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
-PENABLE and PSEL deassert when PREADY is HIGH
-</t>
-  </si>
-  <si>
     <t>APB Response</t>
   </si>
   <si>
@@ -121,16 +116,6 @@
   </si>
   <si>
     <t>Random PSLVERR as returning reponse</t>
-  </si>
-  <si>
-    <t>APB Address</t>
-  </si>
-  <si>
-    <t>PADDR is ONLY aligned address</t>
-  </si>
-  <si>
-    <t>Concurrent Assertion 
-(overlapped assertion)</t>
   </si>
   <si>
     <r>
@@ -370,6 +355,11 @@
       </rPr>
       <t>PSLVERR</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
+PENABLE deassert when PREADY is HIGH
+</t>
   </si>
 </sst>
 </file>
@@ -537,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -586,7 +576,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -933,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{676EAC3C-D51A-4C9A-9C98-285499BC1E5A}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="17.796875" customWidth="1"/>
@@ -988,8 +977,8 @@
       <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>32</v>
+      <c r="E3" s="19" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="117.6">
@@ -1005,14 +994,14 @@
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="67.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
@@ -1020,14 +1009,14 @@
       <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="21"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" ht="184.8">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>21</v>
@@ -1035,14 +1024,14 @@
       <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="21"/>
     </row>
-    <row r="7" spans="1:5" ht="67.2">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:5" ht="50.4">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1051,37 +1040,17 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="33.6">
-      <c r="A9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16.8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\MYSELF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144C995C-99A1-4D0D-B2DD-BE57CB2B1C90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE36C4F-43D9-4F90-823F-61BBF5240CA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A9B6BBD-B787-4672-8FCE-7FD02B8C41F3}"/>
   </bookViews>
@@ -76,9 +76,6 @@
 Different ID transactions WRITE RESPONSE and READ DATA CHANNEL could be returned to any order of issue</t>
   </si>
   <si>
-    <t>Random-constrained for ID</t>
-  </si>
-  <si>
     <t>Define coverpoint of AWID, ARID, BID, RID</t>
   </si>
   <si>
@@ -208,10 +205,6 @@
       </rPr>
       <t xml:space="preserve"> be aligned address</t>
     </r>
-  </si>
-  <si>
-    <t>using ASSOCIATE ARRAY to store and compare transaction
-in Scoreboard</t>
   </si>
   <si>
     <r>
@@ -360,6 +353,13 @@
     <t xml:space="preserve">PENABLE must assert after PSEL one cycle
 PENABLE deassert when PREADY is HIGH
 </t>
+  </si>
+  <si>
+    <t>using ASSOCIATE ARRAY to store, calculate reference model  and compare transaction
+in Scoreboard</t>
+  </si>
+  <si>
+    <t>Randomize ID</t>
   </si>
 </sst>
 </file>
@@ -978,60 +978,60 @@
         <v>12</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="117.6">
       <c r="A4" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="67.2">
       <c r="A5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" ht="184.8">
       <c r="A6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" ht="50.4">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1041,13 +1041,13 @@
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
       <c r="A8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>

--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\MYSELF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DV\AXI2APB\WORK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE36C4F-43D9-4F90-823F-61BBF5240CA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB38C54-82D8-4E1D-80EE-0CAC58DC322B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8A9B6BBD-B787-4672-8FCE-7FD02B8C41F3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>LABEL</t>
   </si>
@@ -46,17 +46,10 @@
   </si>
   <si>
     <t>Concurrent Assertion</t>
-  </si>
-  <si>
-    <t>After reset 
-AWVALID, ARVALID, RVALID, WVALID, BVALID, PSEL, PENABLE  are LOW</t>
   </si>
   <si>
     <t>Generate directed reset before running simulation
 Insert run-time reset during simulation</t>
-  </si>
-  <si>
-    <t>Burst</t>
   </si>
   <si>
     <t>FIXED, INCR, WRAP</t>
@@ -71,11 +64,6 @@
 Cross coverage to check relationship between BURST and LEN</t>
   </si>
   <si>
-    <t>ID belongs to between 0 - 255
-Same ID transactions WRITE RESPONSE CHANNEL and READ DATA CHANNEL must be properly returned to order of issue 
-Different ID transactions WRITE RESPONSE and READ DATA CHANNEL could be returned to any order of issue</t>
-  </si>
-  <si>
     <t>Define coverpoint of AWID, ARID, BID, RID</t>
   </si>
   <si>
@@ -97,9 +85,6 @@
   </si>
   <si>
     <t>Directed test to check each response type</t>
-  </si>
-  <si>
-    <t>Define coverpoint of BRESP, RRESP</t>
   </si>
   <si>
     <t>APB Interface</t>
@@ -205,6 +190,91 @@
       </rPr>
       <t xml:space="preserve"> be aligned address</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
+PENABLE deassert when PREADY is HIGH
+</t>
+  </si>
+  <si>
+    <t>Randomize ID</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">After reset 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AXI slave interface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: 
+RVALID, BVALID must be low
+Write pointer and Read pointer of all FIFOs must be zero
+Addr_reg register in arbiter module must be zero
+Abt_cs register is ABT_IDLE
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>APB master interface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 
+PSEL, PENABLE must be low
+apb_cs register is APB_IDLE</t>
+    </r>
+  </si>
+  <si>
+    <t>Define coverpoint of reset</t>
+  </si>
+  <si>
+    <t>Burst type</t>
+  </si>
+  <si>
+    <t>ID belongs to between 0 - 255
+Same ID transactions of WRITE RESPONSE CHANNEL and READ DATA CHANNEL must be properly returned to order of issue 
+Different ID transactions WRITE RESPONSE and READ DATA CHANNEL could be returned to any order of issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define coverpoint of BRESP, RRESP
+</t>
+  </si>
+  <si>
+    <t>Using Queues to store request information and AXI write data
+Using ASSOCIATIVE array to store AXI read data and AXI write reponse
+Using uvm_tlm_analysis_fifo to store APB transaction
+Calculate AXI address and other information to compare to APB transaction</t>
+  </si>
+  <si>
+    <t>Compare response in scoreboard</t>
   </si>
   <si>
     <r>
@@ -235,7 +305,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> those ranges -&gt; </t>
+      <t xml:space="preserve"> those ranges =&gt; </t>
     </r>
     <r>
       <rPr>
@@ -245,7 +315,8 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>DECERR</t>
+      <t xml:space="preserve">DECERR
+</t>
     </r>
     <r>
       <rPr>
@@ -276,17 +347,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>unaligned address</t>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unaligned address</t>
     </r>
     <r>
       <rPr>
@@ -336,7 +408,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> =&gt; </t>
+      <t xml:space="preserve"> 
+=&gt; </t>
     </r>
     <r>
       <rPr>
@@ -348,18 +421,6 @@
       </rPr>
       <t>PSLVERR</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">PENABLE must assert after PSEL one cycle
-PENABLE deassert when PREADY is HIGH
-</t>
-  </si>
-  <si>
-    <t>using ASSOCIATE ARRAY to store, calculate reference model  and compare transaction
-in Scoreboard</t>
-  </si>
-  <si>
-    <t>Randomize ID</t>
   </si>
 </sst>
 </file>
@@ -539,13 +600,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -562,9 +619,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -587,6 +641,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -926,131 +989,135 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="17.796875" customWidth="1"/>
-    <col min="2" max="2" width="53.19921875" customWidth="1"/>
+    <col min="2" max="2" width="57.19921875" customWidth="1"/>
     <col min="3" max="3" width="50.796875" customWidth="1"/>
-    <col min="4" max="4" width="48.19921875" customWidth="1"/>
-    <col min="5" max="5" width="31.19921875" customWidth="1"/>
+    <col min="4" max="4" width="43.5" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="50.4">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:5" ht="151.19999999999999">
+      <c r="A2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="81.599999999999994" customHeight="1">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="134.4">
+      <c r="A4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="117.6">
-      <c r="A4" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="20"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" ht="67.2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="1:5" ht="218.4">
+      <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:5" ht="184.8">
-      <c r="A6" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="21"/>
+      <c r="D6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" ht="50.4">
-      <c r="A7" s="18" t="s">
-        <v>22</v>
+      <c r="A7" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="39" customHeight="1">
-      <c r="A8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>24</v>
+      <c r="A8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
